--- a/data/trans_camb/P3A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 15,35</t>
+          <t>-9,08; 13,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 2,34</t>
+          <t>-21,02; 1,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,28; 65,03</t>
+          <t>44,72; 66,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 5,73</t>
+          <t>-17,1; 5,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 0,59</t>
+          <t>-21,45; 0,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,41; 57,77</t>
+          <t>36,57; 59,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 6,64</t>
+          <t>-9,39; 6,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,65; -2,38</t>
+          <t>-16,63; -2,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,81; 58,79</t>
+          <t>43,92; 58,59</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 58,48</t>
+          <t>-23,96; 50,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 8,88</t>
+          <t>-50,39; 7,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105,64; 250,83</t>
+          <t>106,38; 254,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 19,17</t>
+          <t>-39,88; 20,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,68; 2,23</t>
+          <t>-50,94; 0,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,93; 200,22</t>
+          <t>84,64; 203,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 21,85</t>
+          <t>-24,05; 21,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,09; -7,5</t>
+          <t>-43,64; -6,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>109,38; 195,25</t>
+          <t>111,13; 198,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 6,9</t>
+          <t>-9,93; 6,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 2,06</t>
+          <t>-13,8; 1,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,36; 55,05</t>
+          <t>39,13; 54,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 5,22</t>
+          <t>-10,88; 4,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 8,84</t>
+          <t>-5,72; 9,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,22; 62,68</t>
+          <t>48,87; 62,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 2,77</t>
+          <t>-7,96; 3,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 3,0</t>
+          <t>-7,02; 4,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46,32; 56,72</t>
+          <t>46,84; 56,91</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 21,64</t>
+          <t>-25,47; 19,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 6,5</t>
+          <t>-35,34; 4,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99,78; 182,39</t>
+          <t>96,25; 177,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 17,34</t>
+          <t>-29,53; 14,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 29,99</t>
+          <t>-15,29; 31,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>128,38; 221,24</t>
+          <t>126,28; 217,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 8,75</t>
+          <t>-21,72; 11,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 9,25</t>
+          <t>-19,1; 13,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>121,29; 183,19</t>
+          <t>124,5; 184,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 3,85</t>
+          <t>-18,67; 4,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 5,81</t>
+          <t>-15,21; 6,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,75; 55,94</t>
+          <t>36,45; 55,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 5,26</t>
+          <t>-15,8; 5,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 7,74</t>
+          <t>-12,62; 7,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,5; 54,12</t>
+          <t>36,12; 54,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 2,29</t>
+          <t>-14,53; 1,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 4,22</t>
+          <t>-10,37; 4,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,38; 52,76</t>
+          <t>39,63; 52,82</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,91; 11,06</t>
+          <t>-39,59; 12,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 16,95</t>
+          <t>-30,98; 18,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,91; 164,36</t>
+          <t>72,39; 163,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,47; 16,63</t>
+          <t>-38,15; 17,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 24,42</t>
+          <t>-29,61; 23,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82,15; 178,38</t>
+          <t>81,71; 179,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 7,21</t>
+          <t>-34,03; 5,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 12,71</t>
+          <t>-24,29; 12,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87,61; 152,29</t>
+          <t>87,15; 156,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 9,36</t>
+          <t>-8,89; 10,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 15,13</t>
+          <t>-4,57; 15,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43,91; 60,43</t>
+          <t>43,91; 60,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 13,91</t>
+          <t>-3,76; 14,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 6,81</t>
+          <t>-11,57; 7,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,12; 55,82</t>
+          <t>42,22; 56,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 9,14</t>
+          <t>-4,04; 9,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 8,16</t>
+          <t>-4,89; 8,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45,39; 56,16</t>
+          <t>45,48; 55,98</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 33,01</t>
+          <t>-25,06; 36,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 56,93</t>
+          <t>-12,82; 54,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116,03; 224,75</t>
+          <t>117,36; 227,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 42,72</t>
+          <t>-9,77; 43,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,35; 19,58</t>
+          <t>-29,12; 21,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>96,71; 176,04</t>
+          <t>97,23; 180,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 28,54</t>
+          <t>-10,44; 30,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 25,47</t>
+          <t>-13,31; 25,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>116,58; 181,6</t>
+          <t>118,5; 179,48</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 4,2</t>
+          <t>-5,96; 4,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 1,52</t>
+          <t>-7,44; 2,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45,29; 54,56</t>
+          <t>46,21; 54,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 2,28</t>
+          <t>-7,0; 2,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 1,71</t>
+          <t>-7,09; 2,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,15; 54,12</t>
+          <t>46,52; 54,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 1,99</t>
+          <t>-4,86; 1,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 0,69</t>
+          <t>-6,07; 0,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47,46; 53,16</t>
+          <t>47,18; 53,37</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 12,82</t>
+          <t>-15,9; 11,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 4,43</t>
+          <t>-20,07; 6,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115,97; 169,33</t>
+          <t>120,52; 167,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 6,92</t>
+          <t>-18,68; 7,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 5,34</t>
+          <t>-18,7; 6,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>118,28; 165,08</t>
+          <t>121,04; 166,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 6,01</t>
+          <t>-12,96; 5,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 2,12</t>
+          <t>-16,37; 1,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>126,38; 159,12</t>
+          <t>125,01; 159,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 13,95</t>
+          <t>-9,24; 14,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,02; 1,77</t>
+          <t>-19,96; 1,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,72; 66,79</t>
+          <t>43,91; 66,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 5,68</t>
+          <t>-16,22; 4,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 0,26</t>
+          <t>-20,85; 0,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,57; 59,33</t>
+          <t>35,32; 58,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 6,59</t>
+          <t>-8,69; 7,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,63; -2,05</t>
+          <t>-17,12; -1,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,92; 58,59</t>
+          <t>43,78; 58,82</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 50,4</t>
+          <t>-22,2; 54,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,39; 7,44</t>
+          <t>-49,98; 6,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106,38; 254,41</t>
+          <t>105,79; 258,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,88; 20,39</t>
+          <t>-37,94; 16,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,94; 0,73</t>
+          <t>-49,89; 3,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,64; 203,01</t>
+          <t>81,07; 203,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 21,69</t>
+          <t>-22,37; 23,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,64; -6,59</t>
+          <t>-43,29; -3,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>111,13; 198,76</t>
+          <t>108,68; 199,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 6,3</t>
+          <t>-9,57; 6,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 1,3</t>
+          <t>-13,79; 1,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,13; 54,69</t>
+          <t>38,77; 54,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 4,48</t>
+          <t>-10,54; 5,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 9,04</t>
+          <t>-6,15; 9,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,87; 62,53</t>
+          <t>49,04; 62,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 3,5</t>
+          <t>-7,78; 3,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 4,06</t>
+          <t>-8,27; 3,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46,84; 56,91</t>
+          <t>46,69; 57,48</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,47; 19,44</t>
+          <t>-24,28; 22,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 4,08</t>
+          <t>-36,18; 5,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96,25; 177,61</t>
+          <t>97,31; 179,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,53; 14,98</t>
+          <t>-28,41; 17,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 31,74</t>
+          <t>-16,55; 31,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>126,28; 217,1</t>
+          <t>126,48; 219,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 11,48</t>
+          <t>-21,04; 11,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 13,18</t>
+          <t>-21,84; 11,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>124,5; 184,91</t>
+          <t>125,04; 189,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 4,4</t>
+          <t>-18,55; 5,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 6,52</t>
+          <t>-16,56; 5,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,45; 55,54</t>
+          <t>36,85; 55,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 5,35</t>
+          <t>-14,98; 6,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 7,56</t>
+          <t>-11,65; 8,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,12; 54,8</t>
+          <t>36,49; 55,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 1,87</t>
+          <t>-13,6; 1,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 4,45</t>
+          <t>-10,58; 4,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,63; 52,82</t>
+          <t>39,79; 52,06</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,59; 12,98</t>
+          <t>-40,19; 16,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 18,97</t>
+          <t>-33,33; 17,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72,39; 163,21</t>
+          <t>75,01; 165,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,15; 17,37</t>
+          <t>-34,94; 19,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 23,75</t>
+          <t>-27,66; 27,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,71; 179,25</t>
+          <t>84,61; 188,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 5,39</t>
+          <t>-31,41; 4,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 12,49</t>
+          <t>-24,61; 11,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87,15; 156,83</t>
+          <t>89,47; 151,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 10,19</t>
+          <t>-8,53; 9,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 15,2</t>
+          <t>-4,13; 15,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43,91; 60,16</t>
+          <t>43,89; 61,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 14,85</t>
+          <t>-4,14; 14,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 7,19</t>
+          <t>-13,08; 6,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,22; 56,65</t>
+          <t>41,45; 56,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 9,5</t>
+          <t>-3,71; 9,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 8,4</t>
+          <t>-5,44; 7,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45,48; 55,98</t>
+          <t>45,24; 56,55</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 36,27</t>
+          <t>-24,15; 35,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 54,26</t>
+          <t>-11,65; 53,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>117,36; 227,17</t>
+          <t>118,32; 227,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 43,03</t>
+          <t>-9,72; 44,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,12; 21,03</t>
+          <t>-31,55; 19,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>97,23; 180,66</t>
+          <t>95,57; 183,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 30,18</t>
+          <t>-9,87; 30,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 25,78</t>
+          <t>-14,82; 24,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>118,5; 179,48</t>
+          <t>116,39; 186,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 4,02</t>
+          <t>-6,15; 3,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 2,15</t>
+          <t>-7,17; 2,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46,21; 54,72</t>
+          <t>45,7; 55,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 2,52</t>
+          <t>-6,69; 2,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 2,08</t>
+          <t>-6,88; 2,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,52; 54,27</t>
+          <t>46,23; 54,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 1,97</t>
+          <t>-4,78; 2,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 0,52</t>
+          <t>-6,36; 0,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47,18; 53,37</t>
+          <t>47,43; 53,5</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 11,94</t>
+          <t>-16,22; 11,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 6,49</t>
+          <t>-19,14; 6,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>120,52; 167,99</t>
+          <t>118,79; 173,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 7,94</t>
+          <t>-17,66; 8,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 6,28</t>
+          <t>-18,53; 7,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>121,04; 166,46</t>
+          <t>119,8; 167,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 5,72</t>
+          <t>-12,91; 6,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 1,51</t>
+          <t>-17,18; 1,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>125,01; 159,86</t>
+          <t>126,73; 161,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-5,5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-10,35</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46,88</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-9,01</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>55,37</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-10,35</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,71</t>
+          <t>56,08</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>51,38</t>
+          <t>51,46</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 14,04</t>
+          <t>-16,11; 5,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 1,62</t>
+          <t>-22,1; 0,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,91; 66,13</t>
+          <t>35,5; 57,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 4,68</t>
+          <t>-8,24; 15,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 0,91</t>
+          <t>-20,12; 2,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,32; 58,31</t>
+          <t>45,07; 65,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 7,25</t>
+          <t>-8,64; 6,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,12; -1,14</t>
+          <t>-17,65; -2,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,78; 58,82</t>
+          <t>43,87; 58,6</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-15,19%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-28,61%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>129,56%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,47%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-26,63%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>163,64%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-15,19%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-28,61%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>131,86%</t>
+          <t>165,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>146,47%</t>
+          <t>146,71%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 54,09</t>
+          <t>-39,07; 19,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,98; 6,67</t>
+          <t>-51,68; 2,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105,79; 258,76</t>
+          <t>82,24; 197,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,94; 16,26</t>
+          <t>-19,51; 58,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,89; 3,02</t>
+          <t>-50,55; 8,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,07; 203,75</t>
+          <t>106,25; 250,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 23,56</t>
+          <t>-22,42; 21,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,29; -3,57</t>
+          <t>-45,09; -7,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>108,68; 199,78</t>
+          <t>109,53; 196,13</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,01</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,18</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>56,13</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,59</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-6,33</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47,38</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,01</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,41</t>
+          <t>48,59</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>52,12</t>
+          <t>52,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 6,76</t>
+          <t>-10,27; 5,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 1,74</t>
+          <t>-6,99; 8,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,77; 54,84</t>
+          <t>48,97; 62,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 5,02</t>
+          <t>-10,36; 6,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 9,27</t>
+          <t>-15,09; 2,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,04; 62,52</t>
+          <t>40,93; 55,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 3,58</t>
+          <t>-8,7; 2,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 3,52</t>
+          <t>-8,23; 3,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46,69; 57,48</t>
+          <t>47,05; 57,01</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-9,09%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>169,32%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-4,49%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-17,84%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>133,57%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-9,09%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>170,16%</t>
+          <t>137,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>151,94%</t>
+          <t>152,94%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 22,16</t>
+          <t>-27,89; 17,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 5,21</t>
+          <t>-19,21; 29,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,31; 179,4</t>
+          <t>127,87; 220,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 17,41</t>
+          <t>-26,18; 21,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 31,66</t>
+          <t>-36,24; 6,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>126,48; 219,68</t>
+          <t>102,2; 185,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 11,4</t>
+          <t>-23,0; 8,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 11,22</t>
+          <t>-22,6; 9,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125,04; 189,62</t>
+          <t>122,88; 184,2</t>
         </is>
       </c>
     </row>
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,81</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,07</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45,07</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-7,94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,87</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>46,82</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,81</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,07</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>46,19</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-6,17</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-3,2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>45,65</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-6,17</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-3,2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>46,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 5,27</t>
+          <t>-15,7; 5,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 5,83</t>
+          <t>-12,34; 7,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,85; 55,4</t>
+          <t>35,73; 53,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 6,05</t>
+          <t>-18,98; 3,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 8,5</t>
+          <t>-15,12; 5,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,49; 55,01</t>
+          <t>36,05; 55,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 1,65</t>
+          <t>-13,22; 2,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 4,3</t>
+          <t>-10,3; 4,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,79; 52,06</t>
+          <t>38,82; 52,05</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-12,9%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-5,55%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>120,98%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-18,78%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-11,51%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>110,73%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-12,9%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-5,55%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>122,54%</t>
+          <t>109,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>116,69%</t>
+          <t>115,44%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,19; 16,42</t>
+          <t>-37,47; 16,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 17,11</t>
+          <t>-28,44; 24,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,01; 165,43</t>
+          <t>80,65; 176,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,94; 19,04</t>
+          <t>-40,91; 11,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 27,58</t>
+          <t>-31,07; 16,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84,61; 188,61</t>
+          <t>70,31; 162,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 4,79</t>
+          <t>-30,15; 7,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 11,95</t>
+          <t>-23,18; 12,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89,47; 151,27</t>
+          <t>86,59; 151,09</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>49,39</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,58</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5,55</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>52,63</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,12</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,15</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,31</t>
+          <t>53,86</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>51,05</t>
+          <t>51,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 9,83</t>
+          <t>-4,19; 13,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 15,34</t>
+          <t>-12,14; 6,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43,89; 61,04</t>
+          <t>42,14; 55,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 14,52</t>
+          <t>-8,04; 9,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 6,52</t>
+          <t>-3,37; 15,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,45; 56,91</t>
+          <t>45,97; 60,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 9,79</t>
+          <t>-4,34; 9,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 7,79</t>
+          <t>-5,15; 8,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45,24; 56,55</t>
+          <t>46,25; 56,63</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13,62%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-8,38%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>131,47%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>17,29%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>164,01%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13,62%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-8,38%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>131,25%</t>
+          <t>167,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>146,7%</t>
+          <t>148,52%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 35,12</t>
+          <t>-10,05; 42,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 53,86</t>
+          <t>-30,35; 19,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118,32; 227,18</t>
+          <t>96,85; 175,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 44,83</t>
+          <t>-23,6; 33,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 19,42</t>
+          <t>-9,13; 56,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>95,57; 183,38</t>
+          <t>121,69; 225,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 30,14</t>
+          <t>-11,52; 28,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 24,21</t>
+          <t>-13,87; 25,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>116,39; 186,14</t>
+          <t>118,54; 184,8</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,61</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>50,18</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-2,83</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>50,43</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,61</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,47</t>
+          <t>51,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>50,46</t>
+          <t>50,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,87</t>
+          <t>-7,64; 2,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 2,15</t>
+          <t>-7,6; 1,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45,7; 55,15</t>
+          <t>45,66; 53,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 2,73</t>
+          <t>-5,59; 4,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 2,56</t>
+          <t>-7,89; 1,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,23; 54,45</t>
+          <t>46,14; 55,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 2,22</t>
+          <t>-5,01; 1,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 0,38</t>
+          <t>-5,93; 0,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47,43; 53,5</t>
+          <t>47,75; 53,13</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-5,44%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-7,32%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>140,57%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-2,83%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-7,99%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>142,58%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-5,44%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-7,32%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>141,39%</t>
+          <t>144,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>141,99%</t>
+          <t>142,54%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 11,55</t>
+          <t>-20,19; 6,92</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 6,48</t>
+          <t>-19,78; 5,34</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118,79; 173,53</t>
+          <t>117,16; 164,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 8,13</t>
+          <t>-14,93; 12,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 7,6</t>
+          <t>-21,13; 4,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>119,8; 167,91</t>
+          <t>118,38; 170,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 6,75</t>
+          <t>-13,32; 6,01</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 1,16</t>
+          <t>-16,0; 2,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>126,73; 161,12</t>
+          <t>127,14; 159,94</t>
         </is>
       </c>
     </row>
